--- a/glaze_ingredients.xlsx
+++ b/glaze_ingredients.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueyiwen/ywshiue/陶藝相關資訊/釉藥配方/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueyiwen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59871DFE-8657-9647-8F03-E0CFA0156D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBC4227-4C37-8449-B47E-0F9B7FE943AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16280" xr2:uid="{1550BD0F-0B9F-E643-9813-E1929A6103CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="91">
   <si>
     <t>成分名稱</t>
   </si>
@@ -53,12 +53,6 @@
     <t>氧化矽</t>
   </si>
   <si>
-    <t>氧化物</t>
-  </si>
-  <si>
-    <t>基本成分</t>
-  </si>
-  <si>
     <t>氧化鋁</t>
   </si>
   <si>
@@ -74,9 +68,6 @@
     <t>氧化鉛</t>
   </si>
   <si>
-    <t>顏色調整</t>
-  </si>
-  <si>
     <t>氧化鈷</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
   </si>
   <si>
     <t>A200長石</t>
-  </si>
-  <si>
-    <t>配料</t>
   </si>
   <si>
     <t>日化長石</t>
@@ -250,13 +238,100 @@
   </si>
   <si>
     <t>其他</t>
+  </si>
+  <si>
+    <t>合成藁灰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SiO₂</t>
+  </si>
+  <si>
+    <t>RO₂</t>
+  </si>
+  <si>
+    <t>酸性氧化物</t>
+  </si>
+  <si>
+    <t>Al₂O₃</t>
+  </si>
+  <si>
+    <t>R₂O₃</t>
+  </si>
+  <si>
+    <t>中間氧化物</t>
+  </si>
+  <si>
+    <t>鹼土氧化物</t>
+  </si>
+  <si>
+    <t>Fe₂O₃</t>
+  </si>
+  <si>
+    <t>變價氧化物</t>
+  </si>
+  <si>
+    <t>P₂O₅</t>
+  </si>
+  <si>
+    <t>K₂O</t>
+  </si>
+  <si>
+    <t>鹼金屬氧化物</t>
+  </si>
+  <si>
+    <t>Na₂O</t>
+  </si>
+  <si>
+    <r>
+      <t>RO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成土灰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>揮發性氧化物</t>
+  </si>
+  <si>
+    <t>玻璃質</t>
+  </si>
+  <si>
+    <t>黏稠劑</t>
+  </si>
+  <si>
+    <t>助熔劑</t>
+  </si>
+  <si>
+    <t>深藍～鈷藍</t>
+  </si>
+  <si>
+    <t>綠／青綠（氧化）、紅（還原）</t>
+  </si>
+  <si>
+    <t>棕紫～深褐～黑褐</t>
+  </si>
+  <si>
+    <t>黃褐～紅褐～深棕</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -280,6 +355,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -645,14 +727,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9EC9A4E-01A3-D948-B187-798B74189E35}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -660,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -683,10 +764,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -695,21 +776,21 @@
         <v>60.08</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -718,21 +799,21 @@
         <v>101.96</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -741,21 +822,21 @@
         <v>56.08</v>
       </c>
       <c r="F4" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -764,21 +845,21 @@
         <v>61.98</v>
       </c>
       <c r="F5" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -787,21 +868,21 @@
         <v>94.2</v>
       </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -810,21 +891,21 @@
         <v>223.2</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -833,21 +914,21 @@
         <v>74.930000000000007</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -856,21 +937,21 @@
         <v>63.55</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -879,21 +960,21 @@
         <v>86.94</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -902,21 +983,21 @@
         <v>81.38</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D12">
         <v>15</v>
@@ -925,21 +1006,21 @@
         <v>61.98</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -948,21 +1029,21 @@
         <v>94.2</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14">
         <v>20</v>
@@ -971,21 +1052,21 @@
         <v>101.96</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15">
         <v>55</v>
@@ -994,21 +1075,21 @@
         <v>60.08</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>14.5</v>
@@ -1017,21 +1098,21 @@
         <v>61.98</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1040,21 +1121,21 @@
         <v>94.2</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D18">
         <v>19.5</v>
@@ -1063,21 +1144,21 @@
         <v>101.96</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D19">
         <v>57</v>
@@ -1086,21 +1167,21 @@
         <v>60.08</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -1109,21 +1190,21 @@
         <v>60.08</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D21">
         <v>27</v>
@@ -1132,21 +1213,21 @@
         <v>56.08</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D22">
         <v>27</v>
@@ -1155,21 +1236,21 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D23">
         <v>46</v>
@@ -1178,21 +1259,21 @@
         <v>44.01</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D24">
         <v>27</v>
@@ -1201,21 +1282,21 @@
         <v>56.08</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>27</v>
@@ -1224,21 +1305,21 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D26">
         <v>46</v>
@@ -1247,21 +1328,21 @@
         <v>44.01</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D27">
         <v>35</v>
@@ -1270,21 +1351,21 @@
         <v>123.22</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D28">
         <v>65</v>
@@ -1293,21 +1374,21 @@
         <v>60.08</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -1316,21 +1397,21 @@
         <v>56.08</v>
       </c>
       <c r="F29" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -1339,21 +1420,21 @@
         <v>61.98</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D31">
         <v>10</v>
@@ -1362,21 +1443,21 @@
         <v>94.2</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>20</v>
@@ -1385,21 +1466,21 @@
         <v>101.96</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D33">
         <v>55</v>
@@ -1408,21 +1489,21 @@
         <v>60.08</v>
       </c>
       <c r="F33" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -1431,21 +1512,21 @@
         <v>79.900000000000006</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -1454,21 +1535,21 @@
         <v>223.2</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1477,21 +1558,21 @@
         <v>81.38</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -1500,21 +1581,21 @@
         <v>118.71</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D38">
         <v>33</v>
@@ -1523,21 +1604,21 @@
         <v>101.96</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G38" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -1546,21 +1627,21 @@
         <v>60.08</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G39" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D40">
         <v>34</v>
@@ -1569,21 +1650,21 @@
         <v>18.02</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D41">
         <v>33</v>
@@ -1592,21 +1673,21 @@
         <v>101.96</v>
       </c>
       <c r="F41" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G41" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D42">
         <v>33</v>
@@ -1615,21 +1696,21 @@
         <v>60.08</v>
       </c>
       <c r="F42" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G42" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D43">
         <v>34</v>
@@ -1638,21 +1719,21 @@
         <v>159.69</v>
       </c>
       <c r="F43" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D44">
         <v>33</v>
@@ -1661,21 +1742,21 @@
         <v>101.96</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D45">
         <v>33</v>
@@ -1684,21 +1765,21 @@
         <v>60.08</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G45" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>34</v>
@@ -1707,21 +1788,21 @@
         <v>159.69</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -1730,21 +1811,21 @@
         <v>60.08</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G47" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D48">
         <v>33</v>
@@ -1753,21 +1834,21 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F48" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D49">
         <v>33</v>
@@ -1776,21 +1857,21 @@
         <v>60.08</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G49" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D50">
         <v>34</v>
@@ -1799,21 +1880,21 @@
         <v>18.02</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1822,21 +1903,21 @@
         <v>56.08</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G51" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D52">
         <v>50</v>
@@ -1845,21 +1926,21 @@
         <v>69.62</v>
       </c>
       <c r="F52" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G52" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D53">
         <v>50</v>
@@ -1868,21 +1949,21 @@
         <v>56.08</v>
       </c>
       <c r="F53" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G53" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D54">
         <v>50</v>
@@ -1891,21 +1972,21 @@
         <v>44.01</v>
       </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G54" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D55">
         <v>50</v>
@@ -1914,21 +1995,21 @@
         <v>56.08</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D56">
         <v>50</v>
@@ -1937,21 +2018,21 @@
         <v>44.01</v>
       </c>
       <c r="F56" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D57">
         <v>50</v>
@@ -1960,21 +2041,21 @@
         <v>29.88</v>
       </c>
       <c r="F57" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D58">
         <v>50</v>
@@ -1983,21 +2064,21 @@
         <v>44.01</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G58" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>50</v>
@@ -2006,21 +2087,21 @@
         <v>153.33000000000001</v>
       </c>
       <c r="F59" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G59" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D60">
         <v>50</v>
@@ -2029,21 +2110,21 @@
         <v>44.01</v>
       </c>
       <c r="F60" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G60" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D61">
         <v>50</v>
@@ -2052,21 +2133,21 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G61" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D62">
         <v>50</v>
@@ -2075,21 +2156,21 @@
         <v>44.01</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G62" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D63">
         <v>50</v>
@@ -2098,21 +2179,21 @@
         <v>103.62</v>
       </c>
       <c r="F63" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="G63" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D64">
         <v>50</v>
@@ -2121,21 +2202,21 @@
         <v>44.01</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G64" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D65">
         <v>20</v>
@@ -2144,21 +2225,21 @@
         <v>29.88</v>
       </c>
       <c r="F65" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
         <v>41</v>
       </c>
-      <c r="B66" t="s">
-        <v>45</v>
-      </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D66">
         <v>30</v>
@@ -2167,21 +2248,21 @@
         <v>101.96</v>
       </c>
       <c r="F66" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D67">
         <v>50</v>
@@ -2190,21 +2271,21 @@
         <v>60.08</v>
       </c>
       <c r="F67" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G67" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -2213,21 +2294,21 @@
         <v>61.98</v>
       </c>
       <c r="F68" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -2236,21 +2317,21 @@
         <v>94.2</v>
       </c>
       <c r="F69" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C70" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D70">
         <v>20</v>
@@ -2259,21 +2340,21 @@
         <v>101.96</v>
       </c>
       <c r="F70" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D71">
         <v>55</v>
@@ -2282,10 +2363,378 @@
         <v>60.08</v>
       </c>
       <c r="F71" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>6</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72">
+        <v>17.59</v>
+      </c>
+      <c r="E72">
+        <v>60.08</v>
+      </c>
+      <c r="F72" t="s">
+        <v>70</v>
+      </c>
+      <c r="G72" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73">
+        <v>3.13</v>
+      </c>
+      <c r="E73">
+        <v>101.96</v>
+      </c>
+      <c r="F73" t="s">
+        <v>73</v>
+      </c>
+      <c r="G73" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" t="s">
+        <v>65</v>
+      </c>
+      <c r="D74">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="E74">
+        <v>56.08</v>
+      </c>
+      <c r="F74" t="s">
+        <v>74</v>
+      </c>
+      <c r="G74" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75">
+        <v>2.25</v>
+      </c>
+      <c r="E75">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F75" t="s">
+        <v>74</v>
+      </c>
+      <c r="G75" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76">
+        <v>0.31</v>
+      </c>
+      <c r="E76">
+        <v>159.69</v>
+      </c>
+      <c r="F76" t="s">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77">
+        <v>0.81</v>
+      </c>
+      <c r="E77">
+        <v>141.94</v>
+      </c>
+      <c r="F77" t="s">
+        <v>70</v>
+      </c>
+      <c r="G77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>65</v>
+      </c>
+      <c r="D78">
+        <v>0.17</v>
+      </c>
+      <c r="E78">
+        <v>94.2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79">
+        <v>0.06</v>
+      </c>
+      <c r="E79">
+        <v>61.98</v>
+      </c>
+      <c r="F79" t="s">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="E80">
+        <v>60.08</v>
+      </c>
+      <c r="F80" t="s">
+        <v>70</v>
+      </c>
+      <c r="G80" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81">
+        <v>2.71</v>
+      </c>
+      <c r="E81">
+        <v>101.96</v>
+      </c>
+      <c r="F81" t="s">
+        <v>73</v>
+      </c>
+      <c r="G81" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" t="s">
+        <v>65</v>
+      </c>
+      <c r="D82">
+        <v>35.93</v>
+      </c>
+      <c r="E82">
+        <v>56.08</v>
+      </c>
+      <c r="F82" t="s">
+        <v>74</v>
+      </c>
+      <c r="G82" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>53</v>
+      </c>
+      <c r="C83" t="s">
+        <v>65</v>
+      </c>
+      <c r="D83">
+        <v>6.06</v>
+      </c>
+      <c r="E83">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F83" t="s">
+        <v>74</v>
+      </c>
+      <c r="G83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" t="s">
+        <v>72</v>
+      </c>
+      <c r="D84">
+        <v>0.23</v>
+      </c>
+      <c r="E84">
+        <v>159.69</v>
+      </c>
+      <c r="F84" t="s">
+        <v>76</v>
+      </c>
+      <c r="G84" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>82</v>
+      </c>
+      <c r="B85" t="s">
+        <v>77</v>
+      </c>
+      <c r="C85" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85">
+        <v>2.65</v>
+      </c>
+      <c r="E85">
+        <v>141.94</v>
+      </c>
+      <c r="F85" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
+        <v>78</v>
+      </c>
+      <c r="C86" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86">
+        <v>0.15</v>
+      </c>
+      <c r="E86">
+        <v>94.2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>82</v>
+      </c>
+      <c r="B87" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87">
+        <v>0.02</v>
+      </c>
+      <c r="E87">
+        <v>61.98</v>
+      </c>
+      <c r="F87" t="s">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/glaze_ingredients.xlsx
+++ b/glaze_ingredients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueyiwen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBC4227-4C37-8449-B47E-0F9B7FE943AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF6EE2E-726D-DB47-BE19-019C3BC33253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16280" xr2:uid="{1550BD0F-0B9F-E643-9813-E1929A6103CD}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="91">
-  <si>
-    <t>成分名稱</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="96">
   <si>
     <t>類型</t>
   </si>
@@ -247,18 +244,12 @@
     <t>SiO₂</t>
   </si>
   <si>
-    <t>RO₂</t>
-  </si>
-  <si>
     <t>酸性氧化物</t>
   </si>
   <si>
     <t>Al₂O₃</t>
   </si>
   <si>
-    <t>R₂O₃</t>
-  </si>
-  <si>
     <t>中間氧化物</t>
   </si>
   <si>
@@ -281,22 +272,6 @@
   </si>
   <si>
     <t>Na₂O</t>
-  </si>
-  <si>
-    <r>
-      <t>RO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>₂</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>合成土灰</t>
@@ -325,13 +300,49 @@
   </si>
   <si>
     <t>黃褐～紅褐～深棕</t>
+  </si>
+  <si>
+    <t>RO2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>R2O3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成分名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>軸向</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中間氧化物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -355,13 +366,6 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Cambria Math"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -727,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9EC9A4E-01A3-D948-B187-798B74189E35}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -736,38 +740,41 @@
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -776,21 +783,24 @@
         <v>60.08</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -799,21 +809,24 @@
         <v>101.96</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -822,21 +835,24 @@
         <v>56.08</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -845,21 +861,24 @@
         <v>61.98</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -868,21 +887,24 @@
         <v>94.2</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -891,21 +913,24 @@
         <v>223.2</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -914,21 +939,24 @@
         <v>74.930000000000007</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -937,21 +965,24 @@
         <v>63.55</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>84</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -960,21 +991,24 @@
         <v>86.94</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -983,21 +1017,24 @@
         <v>81.38</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12">
         <v>15</v>
@@ -1006,21 +1043,24 @@
         <v>61.98</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1029,21 +1069,24 @@
         <v>94.2</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <v>20</v>
@@ -1052,21 +1095,24 @@
         <v>101.96</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15">
         <v>55</v>
@@ -1075,21 +1121,24 @@
         <v>60.08</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16">
         <v>14.5</v>
@@ -1098,21 +1147,24 @@
         <v>61.98</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1121,21 +1173,24 @@
         <v>94.2</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18">
         <v>19.5</v>
@@ -1144,21 +1199,24 @@
         <v>101.96</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19">
         <v>57</v>
@@ -1167,21 +1225,24 @@
         <v>60.08</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -1190,21 +1251,24 @@
         <v>60.08</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21">
         <v>27</v>
@@ -1213,21 +1277,24 @@
         <v>56.08</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22">
         <v>27</v>
@@ -1236,21 +1303,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23">
         <v>46</v>
@@ -1259,21 +1329,24 @@
         <v>44.01</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24">
         <v>27</v>
@@ -1282,21 +1355,24 @@
         <v>56.08</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25">
         <v>27</v>
@@ -1305,21 +1381,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>46</v>
@@ -1328,21 +1407,24 @@
         <v>44.01</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>35</v>
@@ -1351,21 +1433,24 @@
         <v>123.22</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>65</v>
@@ -1374,21 +1459,24 @@
         <v>60.08</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -1397,21 +1485,24 @@
         <v>56.08</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -1420,21 +1511,24 @@
         <v>61.98</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31">
         <v>10</v>
@@ -1443,21 +1537,24 @@
         <v>94.2</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32">
         <v>20</v>
@@ -1466,21 +1563,24 @@
         <v>101.96</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D33">
         <v>55</v>
@@ -1489,21 +1589,24 @@
         <v>60.08</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -1512,21 +1615,24 @@
         <v>79.900000000000006</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -1535,21 +1641,24 @@
         <v>223.2</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1558,21 +1667,24 @@
         <v>81.38</v>
       </c>
       <c r="F36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -1581,21 +1693,24 @@
         <v>118.71</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D38">
         <v>33</v>
@@ -1604,21 +1719,24 @@
         <v>101.96</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -1627,21 +1745,24 @@
         <v>60.08</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D40">
         <v>34</v>
@@ -1650,21 +1771,24 @@
         <v>18.02</v>
       </c>
       <c r="F40" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D41">
         <v>33</v>
@@ -1673,21 +1797,24 @@
         <v>101.96</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D42">
         <v>33</v>
@@ -1696,21 +1823,24 @@
         <v>60.08</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43">
         <v>34</v>
@@ -1719,21 +1849,24 @@
         <v>159.69</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G43" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44">
         <v>33</v>
@@ -1742,21 +1875,24 @@
         <v>101.96</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D45">
         <v>33</v>
@@ -1765,21 +1901,24 @@
         <v>60.08</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D46">
         <v>34</v>
@@ -1788,21 +1927,24 @@
         <v>159.69</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -1811,21 +1953,24 @@
         <v>60.08</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>33</v>
@@ -1834,21 +1979,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F48" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49">
         <v>33</v>
@@ -1857,21 +2005,24 @@
         <v>60.08</v>
       </c>
       <c r="F49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G49" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50">
         <v>34</v>
@@ -1880,21 +2031,24 @@
         <v>18.02</v>
       </c>
       <c r="F50" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1903,21 +2057,24 @@
         <v>56.08</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52">
         <v>50</v>
@@ -1926,21 +2083,24 @@
         <v>69.62</v>
       </c>
       <c r="F52" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53">
         <v>50</v>
@@ -1949,21 +2109,24 @@
         <v>56.08</v>
       </c>
       <c r="F53" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H53" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54">
         <v>50</v>
@@ -1972,21 +2135,24 @@
         <v>44.01</v>
       </c>
       <c r="F54" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55">
         <v>50</v>
@@ -1995,21 +2161,24 @@
         <v>56.08</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H55" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D56">
         <v>50</v>
@@ -2018,21 +2187,24 @@
         <v>44.01</v>
       </c>
       <c r="F56" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D57">
         <v>50</v>
@@ -2041,21 +2213,24 @@
         <v>29.88</v>
       </c>
       <c r="F57" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H57" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D58">
         <v>50</v>
@@ -2064,21 +2239,24 @@
         <v>44.01</v>
       </c>
       <c r="F58" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H58" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D59">
         <v>50</v>
@@ -2087,21 +2265,24 @@
         <v>153.33000000000001</v>
       </c>
       <c r="F59" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D60">
         <v>50</v>
@@ -2110,21 +2291,24 @@
         <v>44.01</v>
       </c>
       <c r="F60" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61">
         <v>50</v>
@@ -2133,21 +2317,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F61" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G61" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62">
         <v>50</v>
@@ -2156,21 +2343,24 @@
         <v>44.01</v>
       </c>
       <c r="F62" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D63">
         <v>50</v>
@@ -2179,21 +2369,24 @@
         <v>103.62</v>
       </c>
       <c r="F63" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D64">
         <v>50</v>
@@ -2202,21 +2395,24 @@
         <v>44.01</v>
       </c>
       <c r="F64" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D65">
         <v>20</v>
@@ -2225,21 +2421,24 @@
         <v>29.88</v>
       </c>
       <c r="F65" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D66">
         <v>30</v>
@@ -2248,21 +2447,24 @@
         <v>101.96</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="G66" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D67">
         <v>50</v>
@@ -2271,21 +2473,24 @@
         <v>60.08</v>
       </c>
       <c r="F67" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G67" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -2294,21 +2499,24 @@
         <v>61.98</v>
       </c>
       <c r="F68" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -2317,21 +2525,24 @@
         <v>94.2</v>
       </c>
       <c r="F69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70">
         <v>20</v>
@@ -2340,21 +2551,24 @@
         <v>101.96</v>
       </c>
       <c r="F70" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D71">
         <v>55</v>
@@ -2363,21 +2577,24 @@
         <v>60.08</v>
       </c>
       <c r="F71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G71" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" t="s">
         <v>67</v>
       </c>
-      <c r="B72" t="s">
-        <v>68</v>
-      </c>
       <c r="C72" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D72">
         <v>17.59</v>
@@ -2386,21 +2603,24 @@
         <v>60.08</v>
       </c>
       <c r="F72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G72" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C73" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D73">
         <v>3.13</v>
@@ -2409,21 +2629,24 @@
         <v>101.96</v>
       </c>
       <c r="F73" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G73" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D74">
         <v>37.090000000000003</v>
@@ -2432,21 +2655,24 @@
         <v>56.08</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G74" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H74" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D75">
         <v>2.25</v>
@@ -2455,21 +2681,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F75" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G75" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D76">
         <v>0.31</v>
@@ -2478,21 +2707,24 @@
         <v>159.69</v>
       </c>
       <c r="F76" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G76" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="16">
+        <v>86</v>
+      </c>
+      <c r="H76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D77">
         <v>0.81</v>
@@ -2501,21 +2733,24 @@
         <v>141.94</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D78">
         <v>0.17</v>
@@ -2524,21 +2759,24 @@
         <v>94.2</v>
       </c>
       <c r="F78" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D79">
         <v>0.06</v>
@@ -2547,21 +2785,24 @@
         <v>61.98</v>
       </c>
       <c r="F79" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D80">
         <v>17.350000000000001</v>
@@ -2570,21 +2811,24 @@
         <v>60.08</v>
       </c>
       <c r="F80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G80" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D81">
         <v>2.71</v>
@@ -2593,21 +2837,24 @@
         <v>101.96</v>
       </c>
       <c r="F81" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G81" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="H81" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D82">
         <v>35.93</v>
@@ -2616,21 +2863,24 @@
         <v>56.08</v>
       </c>
       <c r="F82" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G82" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H82" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D83">
         <v>6.06</v>
@@ -2639,21 +2889,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F83" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H83" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D84">
         <v>0.23</v>
@@ -2662,21 +2915,24 @@
         <v>159.69</v>
       </c>
       <c r="F84" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G84" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C85" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D85">
         <v>2.65</v>
@@ -2685,21 +2941,24 @@
         <v>141.94</v>
       </c>
       <c r="F85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G85" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D86">
         <v>0.15</v>
@@ -2708,21 +2967,24 @@
         <v>94.2</v>
       </c>
       <c r="F86" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>82</v>
+      </c>
+      <c r="H86" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D87">
         <v>0.02</v>
@@ -2731,10 +2993,13 @@
         <v>61.98</v>
       </c>
       <c r="F87" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s">
-        <v>86</v>
+        <v>82</v>
+      </c>
+      <c r="H87" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/glaze_ingredients.xlsx
+++ b/glaze_ingredients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueyiwen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF6EE2E-726D-DB47-BE19-019C3BC33253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638F5456-B476-AF42-BE20-EE187CCBE130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16280" xr2:uid="{1550BD0F-0B9F-E643-9813-E1929A6103CD}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="96">
-  <si>
-    <t>類型</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="102">
   <si>
     <t>分子量（g/mol）</t>
   </si>
@@ -159,9 +156,6 @@
     <t>SiO2</t>
   </si>
   <si>
-    <t>Al2O3</t>
-  </si>
-  <si>
     <t>CaO</t>
   </si>
   <si>
@@ -186,31 +180,13 @@
     <t>ZnO</t>
   </si>
   <si>
-    <t>TiO2</t>
-  </si>
-  <si>
-    <t>SnO2</t>
-  </si>
-  <si>
     <t>百分比</t>
   </si>
   <si>
     <t>MgO</t>
   </si>
   <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>ZrO2</t>
-  </si>
-  <si>
     <t>H2O</t>
-  </si>
-  <si>
-    <t>Fe2O3</t>
-  </si>
-  <si>
-    <t>B2O3</t>
   </si>
   <si>
     <t>Li2O</t>
@@ -335,6 +311,292 @@
   </si>
   <si>
     <t>中間氧化物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>類型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>變價氧化物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Al</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>₃</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Na</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>TiO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SnO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SiO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₃</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SiO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ZrO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -342,7 +604,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -366,6 +628,20 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -737,44 +1013,45 @@
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -783,24 +1060,24 @@
         <v>60.08</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
-      </c>
-      <c r="H2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -809,24 +1086,24 @@
         <v>101.96</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -835,24 +1112,24 @@
         <v>56.08</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -861,24 +1138,24 @@
         <v>61.98</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -887,24 +1164,24 @@
         <v>94.2</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -913,24 +1190,24 @@
         <v>223.2</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -939,24 +1216,24 @@
         <v>74.930000000000007</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -965,24 +1242,24 @@
         <v>63.55</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -991,24 +1268,24 @@
         <v>86.94</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -1017,24 +1294,24 @@
         <v>81.38</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D12">
         <v>15</v>
@@ -1043,24 +1320,24 @@
         <v>61.98</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1069,24 +1346,24 @@
         <v>94.2</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D14">
         <v>20</v>
@@ -1095,24 +1372,24 @@
         <v>101.96</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>55</v>
@@ -1121,24 +1398,24 @@
         <v>60.08</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <v>14.5</v>
@@ -1147,24 +1424,24 @@
         <v>61.98</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
-      </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -1173,24 +1450,24 @@
         <v>94.2</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D18">
         <v>19.5</v>
@@ -1199,24 +1476,24 @@
         <v>101.96</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D19">
         <v>57</v>
@@ -1225,24 +1502,24 @@
         <v>60.08</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -1251,24 +1528,24 @@
         <v>60.08</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D21">
         <v>27</v>
@@ -1277,24 +1554,24 @@
         <v>56.08</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D22">
         <v>27</v>
@@ -1303,24 +1580,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>46</v>
@@ -1329,24 +1606,24 @@
         <v>44.01</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D24">
         <v>27</v>
@@ -1355,24 +1632,24 @@
         <v>56.08</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>27</v>
@@ -1381,24 +1658,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>46</v>
@@ -1407,24 +1684,24 @@
         <v>44.01</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" t="s">
         <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
       </c>
       <c r="D27">
         <v>35</v>
@@ -1433,24 +1710,24 @@
         <v>123.22</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H27" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D28">
         <v>65</v>
@@ -1459,24 +1736,24 @@
         <v>60.08</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -1485,24 +1762,24 @@
         <v>56.08</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="16">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -1511,24 +1788,24 @@
         <v>61.98</v>
       </c>
       <c r="F30" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D31">
         <v>10</v>
@@ -1537,24 +1814,24 @@
         <v>94.2</v>
       </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D32">
         <v>20</v>
@@ -1563,24 +1840,24 @@
         <v>101.96</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D33">
         <v>55</v>
@@ -1589,24 +1866,24 @@
         <v>60.08</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -1615,24 +1892,24 @@
         <v>79.900000000000006</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H34" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -1641,24 +1918,24 @@
         <v>223.2</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H35" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1667,24 +1944,24 @@
         <v>81.38</v>
       </c>
       <c r="F36" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H36" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="16">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -1693,24 +1970,24 @@
         <v>118.71</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D38">
         <v>33</v>
@@ -1719,24 +1996,24 @@
         <v>101.96</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G38" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H38" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D39">
         <v>33</v>
@@ -1745,24 +2022,24 @@
         <v>60.08</v>
       </c>
       <c r="F39" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H39" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>34</v>
@@ -1771,24 +2048,24 @@
         <v>18.02</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G40" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D41">
         <v>33</v>
@@ -1797,24 +2074,24 @@
         <v>101.96</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G41" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H41" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D42">
         <v>33</v>
@@ -1823,24 +2100,24 @@
         <v>60.08</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H42" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D43">
         <v>34</v>
@@ -1849,24 +2126,24 @@
         <v>159.69</v>
       </c>
       <c r="F43" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D44">
         <v>33</v>
@@ -1875,24 +2152,24 @@
         <v>101.96</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D45">
         <v>33</v>
@@ -1901,24 +2178,24 @@
         <v>60.08</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H45" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D46">
         <v>34</v>
@@ -1927,24 +2204,24 @@
         <v>159.69</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -1953,24 +2230,24 @@
         <v>60.08</v>
       </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H47" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D48">
         <v>33</v>
@@ -1979,24 +2256,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F48" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="16">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D49">
         <v>33</v>
@@ -2005,24 +2282,24 @@
         <v>60.08</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G49" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H49" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="16">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D50">
         <v>34</v>
@@ -2031,24 +2308,24 @@
         <v>18.02</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G50" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2057,24 +2334,24 @@
         <v>56.08</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H51" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="16">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D52">
         <v>50</v>
@@ -2083,24 +2360,24 @@
         <v>69.62</v>
       </c>
       <c r="F52" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G52" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H52" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D53">
         <v>50</v>
@@ -2109,24 +2386,24 @@
         <v>56.08</v>
       </c>
       <c r="F53" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G53" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="16">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D54">
         <v>50</v>
@@ -2135,24 +2412,24 @@
         <v>44.01</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G54" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H54" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D55">
         <v>50</v>
@@ -2161,24 +2438,24 @@
         <v>56.08</v>
       </c>
       <c r="F55" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H55" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="16">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>50</v>
@@ -2187,24 +2464,24 @@
         <v>44.01</v>
       </c>
       <c r="F56" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G56" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="16">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D57">
         <v>50</v>
@@ -2213,24 +2490,24 @@
         <v>29.88</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G57" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H57" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="16">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <v>50</v>
@@ -2239,24 +2516,24 @@
         <v>44.01</v>
       </c>
       <c r="F58" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H58" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D59">
         <v>50</v>
@@ -2265,24 +2542,24 @@
         <v>153.33000000000001</v>
       </c>
       <c r="F59" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H59" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="16">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D60">
         <v>50</v>
@@ -2291,24 +2568,24 @@
         <v>44.01</v>
       </c>
       <c r="F60" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G60" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D61">
         <v>50</v>
@@ -2317,24 +2594,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F61" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H61" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="16">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D62">
         <v>50</v>
@@ -2343,24 +2620,24 @@
         <v>44.01</v>
       </c>
       <c r="F62" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G62" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D63">
         <v>50</v>
@@ -2369,24 +2646,24 @@
         <v>103.62</v>
       </c>
       <c r="F63" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G63" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H63" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="16">
       <c r="A64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D64">
         <v>50</v>
@@ -2395,24 +2672,24 @@
         <v>44.01</v>
       </c>
       <c r="F64" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G64" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H64" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D65">
         <v>20</v>
@@ -2421,24 +2698,24 @@
         <v>29.88</v>
       </c>
       <c r="F65" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G65" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H65" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D66">
         <v>30</v>
@@ -2447,24 +2724,24 @@
         <v>101.96</v>
       </c>
       <c r="F66" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G66" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H66" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D67">
         <v>50</v>
@@ -2473,24 +2750,24 @@
         <v>60.08</v>
       </c>
       <c r="F67" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H67" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -2499,24 +2776,24 @@
         <v>61.98</v>
       </c>
       <c r="F68" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G68" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H68" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -2525,24 +2802,24 @@
         <v>94.2</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H69" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D70">
         <v>20</v>
@@ -2551,24 +2828,24 @@
         <v>101.96</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G70" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H70" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D71">
         <v>55</v>
@@ -2577,24 +2854,24 @@
         <v>60.08</v>
       </c>
       <c r="F71" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G71" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H71" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D72">
         <v>17.59</v>
@@ -2603,24 +2880,24 @@
         <v>60.08</v>
       </c>
       <c r="F72" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H72" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D73">
         <v>3.13</v>
@@ -2629,24 +2906,24 @@
         <v>101.96</v>
       </c>
       <c r="F73" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H73" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D74">
         <v>37.090000000000003</v>
@@ -2655,24 +2932,24 @@
         <v>56.08</v>
       </c>
       <c r="F74" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H74" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D75">
         <v>2.25</v>
@@ -2681,24 +2958,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F75" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G75" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H75" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D76">
         <v>0.31</v>
@@ -2707,24 +2984,24 @@
         <v>159.69</v>
       </c>
       <c r="F76" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
+        <v>58</v>
+      </c>
+      <c r="B77" t="s">
         <v>66</v>
       </c>
-      <c r="B77" t="s">
-        <v>74</v>
-      </c>
       <c r="C77" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D77">
         <v>0.81</v>
@@ -2733,24 +3010,24 @@
         <v>141.94</v>
       </c>
       <c r="F77" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G77" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H77" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C78" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D78">
         <v>0.17</v>
@@ -2759,24 +3036,24 @@
         <v>94.2</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G78" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H78" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C79" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D79">
         <v>0.06</v>
@@ -2785,24 +3062,24 @@
         <v>61.98</v>
       </c>
       <c r="F79" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G79" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H79" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C80" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D80">
         <v>17.350000000000001</v>
@@ -2811,24 +3088,24 @@
         <v>60.08</v>
       </c>
       <c r="F80" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H80" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C81" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D81">
         <v>2.71</v>
@@ -2837,24 +3114,24 @@
         <v>101.96</v>
       </c>
       <c r="F81" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G81" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H81" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C82" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D82">
         <v>35.93</v>
@@ -2863,24 +3140,24 @@
         <v>56.08</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G82" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H82" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D83">
         <v>6.06</v>
@@ -2889,24 +3166,24 @@
         <v>40.299999999999997</v>
       </c>
       <c r="F83" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G83" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H83" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C84" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D84">
         <v>0.23</v>
@@ -2915,24 +3192,24 @@
         <v>159.69</v>
       </c>
       <c r="F84" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="G84" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D85">
         <v>2.65</v>
@@ -2941,24 +3218,24 @@
         <v>141.94</v>
       </c>
       <c r="F85" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G85" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H85" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C86" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D86">
         <v>0.15</v>
@@ -2967,24 +3244,24 @@
         <v>94.2</v>
       </c>
       <c r="F86" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G86" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H86" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D87">
         <v>0.02</v>
@@ -2993,13 +3270,13 @@
         <v>61.98</v>
       </c>
       <c r="F87" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G87" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H87" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/glaze_ingredients.xlsx
+++ b/glaze_ingredients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xueyiwen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638F5456-B476-AF42-BE20-EE187CCBE130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D277355D-6718-4649-BEDD-D0FE4A9531A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16280" xr2:uid="{1550BD0F-0B9F-E643-9813-E1929A6103CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="117">
   <si>
     <t>分子量（g/mol）</t>
   </si>
@@ -232,6 +232,9 @@
     <t>鹼土氧化物</t>
   </si>
   <si>
+    <t>氧化鐵</t>
+  </si>
+  <si>
     <t>Fe₂O₃</t>
   </si>
   <si>
@@ -291,22 +294,6 @@
   </si>
   <si>
     <t>成分名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>軸向</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>X</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -597,6 +584,61 @@
       </rPr>
       <t>₂</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二氧化鈦</t>
+  </si>
+  <si>
+    <t>TiO₂</t>
+  </si>
+  <si>
+    <t>增白、乳濁、黃調強化、結晶觸發</t>
+  </si>
+  <si>
+    <t>二氧化鋯</t>
+  </si>
+  <si>
+    <t>ZrO₂</t>
+  </si>
+  <si>
+    <t>遮蓋、消透明、霧白化、降低發色強度</t>
+  </si>
+  <si>
+    <t>SnO₂</t>
+  </si>
+  <si>
+    <t>乳白、遮蓋、柔化色相、提高不透明度</t>
+  </si>
+  <si>
+    <t>黃褐～紅褐～黑褐（依釉性變化）</t>
+  </si>
+  <si>
+    <t>氧化鎳</t>
+  </si>
+  <si>
+    <t>NiO</t>
+  </si>
+  <si>
+    <t>灰綠、橄欖綠、褐色調整、降低彩度（消色作用）</t>
+  </si>
+  <si>
+    <t>乳濁、增白、結晶觸發、黃色調強化</t>
+  </si>
+  <si>
+    <t>增加遮蓋性、霧化效果、降低透明度</t>
+  </si>
+  <si>
+    <t>提供暖色調（黃、橙、褐），影響釉色偏暖</t>
+  </si>
+  <si>
+    <t>提高釉穩定性、增加黏稠度</t>
+  </si>
+  <si>
+    <t>增加玻璃網絡、提升結構穩定性</t>
+  </si>
+  <si>
+    <t>金紅石</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -666,11 +708,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1007,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9EC9A4E-01A3-D948-B187-798B74189E35}">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -1017,9 +1062,9 @@
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -1034,16 +1079,13 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1051,7 +1093,7 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -1063,21 +1105,18 @@
         <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -1089,13 +1128,10 @@
         <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1103,7 +1139,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1115,18 +1151,15 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>56</v>
@@ -1138,21 +1171,18 @@
         <v>61.98</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>56</v>
@@ -1164,16 +1194,13 @@
         <v>94.2</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1193,13 +1220,10 @@
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1216,16 +1240,13 @@
         <v>74.930000000000007</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1242,16 +1263,13 @@
         <v>63.55</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1268,16 +1286,13 @@
         <v>86.94</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1297,18 +1312,15 @@
         <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -1320,21 +1332,18 @@
         <v>61.98</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
         <v>56</v>
@@ -1346,21 +1355,18 @@
         <v>94.2</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
         <v>55</v>
@@ -1375,13 +1381,10 @@
         <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1401,18 +1404,15 @@
         <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16">
       <c r="A16" t="s">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
@@ -1424,21 +1424,18 @@
         <v>61.98</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
         <v>56</v>
@@ -1450,16 +1447,13 @@
         <v>94.2</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1479,13 +1473,10 @@
         <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1505,13 +1496,10 @@
         <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -1531,13 +1519,10 @@
         <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1557,13 +1542,10 @@
         <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1583,18 +1565,15 @@
         <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16">
       <c r="A23" t="s">
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
         <v>57</v>
@@ -1606,16 +1585,13 @@
         <v>44.01</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1635,13 +1611,10 @@
         <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1661,18 +1634,15 @@
         <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16">
       <c r="A26" t="s">
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
         <v>57</v>
@@ -1684,21 +1654,18 @@
         <v>44.01</v>
       </c>
       <c r="F26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
-      </c>
-      <c r="H26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16">
       <c r="A27" t="s">
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
@@ -1713,13 +1680,10 @@
         <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1739,13 +1703,10 @@
         <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -1765,18 +1726,15 @@
         <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16">
       <c r="A30" t="s">
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
         <v>56</v>
@@ -1788,21 +1746,18 @@
         <v>61.98</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
-      </c>
-      <c r="H30" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16">
       <c r="A31" t="s">
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>56</v>
@@ -1814,21 +1769,18 @@
         <v>94.2</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
-      </c>
-      <c r="H31" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16">
       <c r="A32" t="s">
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
         <v>55</v>
@@ -1843,13 +1795,10 @@
         <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -1869,18 +1818,15 @@
         <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="16">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16">
       <c r="A34" t="s">
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
         <v>54</v>
@@ -1895,13 +1841,10 @@
         <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -1921,13 +1864,10 @@
         <v>63</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
-      </c>
-      <c r="H35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -1947,18 +1887,15 @@
         <v>63</v>
       </c>
       <c r="G36" t="s">
-        <v>74</v>
-      </c>
-      <c r="H36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16">
       <c r="A37" t="s">
         <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
         <v>54</v>
@@ -1973,13 +1910,10 @@
         <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -1999,13 +1933,10 @@
         <v>62</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2025,13 +1956,10 @@
         <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
-      </c>
-      <c r="H39" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2048,16 +1976,13 @@
         <v>18.02</v>
       </c>
       <c r="F40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
-      </c>
-      <c r="H40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>24</v>
       </c>
@@ -2077,13 +2002,10 @@
         <v>62</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
-      </c>
-      <c r="H41" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -2103,18 +2025,15 @@
         <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
         <v>55</v>
@@ -2126,16 +2045,13 @@
         <v>159.69</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -2155,13 +2071,10 @@
         <v>62</v>
       </c>
       <c r="G44" t="s">
-        <v>73</v>
-      </c>
-      <c r="H44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -2181,18 +2094,15 @@
         <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>72</v>
-      </c>
-      <c r="H45" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
         <v>55</v>
@@ -2204,21 +2114,18 @@
         <v>159.69</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G46" t="s">
-        <v>78</v>
-      </c>
-      <c r="H46" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="16">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="16">
       <c r="A47" t="s">
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
         <v>54</v>
@@ -2233,13 +2140,10 @@
         <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>72</v>
-      </c>
-      <c r="H47" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -2259,18 +2163,15 @@
         <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
-      </c>
-      <c r="H48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16">
       <c r="A49" t="s">
         <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
         <v>54</v>
@@ -2285,18 +2186,15 @@
         <v>60</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="16">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16">
       <c r="A50" t="s">
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
         <v>57</v>
@@ -2308,16 +2206,13 @@
         <v>18.02</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G50" t="s">
-        <v>73</v>
-      </c>
-      <c r="H50" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -2337,18 +2232,15 @@
         <v>63</v>
       </c>
       <c r="G51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H51" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16">
       <c r="A52" t="s">
         <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
         <v>55</v>
@@ -2363,13 +2255,10 @@
         <v>62</v>
       </c>
       <c r="G52" t="s">
-        <v>74</v>
-      </c>
-      <c r="H52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>29</v>
       </c>
@@ -2389,18 +2278,15 @@
         <v>63</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
-      </c>
-      <c r="H53" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16">
       <c r="A54" t="s">
         <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
         <v>57</v>
@@ -2412,16 +2298,13 @@
         <v>44.01</v>
       </c>
       <c r="F54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
-      </c>
-      <c r="H54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -2441,18 +2324,15 @@
         <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
-      </c>
-      <c r="H55" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16">
       <c r="A56" t="s">
         <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
         <v>57</v>
@@ -2464,21 +2344,18 @@
         <v>44.01</v>
       </c>
       <c r="F56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G56" t="s">
-        <v>74</v>
-      </c>
-      <c r="H56" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16">
       <c r="A57" t="s">
         <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
         <v>56</v>
@@ -2490,21 +2367,18 @@
         <v>29.88</v>
       </c>
       <c r="F57" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
-      </c>
-      <c r="H57" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16">
       <c r="A58" t="s">
         <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
         <v>57</v>
@@ -2516,16 +2390,13 @@
         <v>44.01</v>
       </c>
       <c r="F58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
-      </c>
-      <c r="H58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -2545,18 +2416,15 @@
         <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>74</v>
-      </c>
-      <c r="H59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16">
       <c r="A60" t="s">
         <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
         <v>57</v>
@@ -2568,16 +2436,13 @@
         <v>44.01</v>
       </c>
       <c r="F60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G60" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>33</v>
       </c>
@@ -2597,18 +2462,15 @@
         <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>74</v>
-      </c>
-      <c r="H61" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16">
       <c r="A62" t="s">
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C62" t="s">
         <v>57</v>
@@ -2620,16 +2482,13 @@
         <v>44.01</v>
       </c>
       <c r="F62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G62" t="s">
-        <v>74</v>
-      </c>
-      <c r="H62" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -2649,18 +2508,15 @@
         <v>63</v>
       </c>
       <c r="G63" t="s">
-        <v>74</v>
-      </c>
-      <c r="H63" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="16">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16">
       <c r="A64" t="s">
         <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
         <v>57</v>
@@ -2672,16 +2528,13 @@
         <v>44.01</v>
       </c>
       <c r="F64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G64" t="s">
-        <v>74</v>
-      </c>
-      <c r="H64" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>35</v>
       </c>
@@ -2698,16 +2551,13 @@
         <v>29.88</v>
       </c>
       <c r="F65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G65" t="s">
-        <v>74</v>
-      </c>
-      <c r="H65" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>35</v>
       </c>
@@ -2724,16 +2574,13 @@
         <v>101.96</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G66" t="s">
-        <v>73</v>
-      </c>
-      <c r="H66" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>35</v>
       </c>
@@ -2753,13 +2600,10 @@
         <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>72</v>
-      </c>
-      <c r="H67" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>36</v>
       </c>
@@ -2776,16 +2620,13 @@
         <v>61.98</v>
       </c>
       <c r="F68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G68" t="s">
-        <v>74</v>
-      </c>
-      <c r="H68" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>36</v>
       </c>
@@ -2802,16 +2643,13 @@
         <v>94.2</v>
       </c>
       <c r="F69" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G69" t="s">
-        <v>74</v>
-      </c>
-      <c r="H69" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>36</v>
       </c>
@@ -2831,13 +2669,10 @@
         <v>62</v>
       </c>
       <c r="G70" t="s">
-        <v>73</v>
-      </c>
-      <c r="H70" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>36</v>
       </c>
@@ -2857,13 +2692,10 @@
         <v>60</v>
       </c>
       <c r="G71" t="s">
-        <v>72</v>
-      </c>
-      <c r="H71" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>58</v>
       </c>
@@ -2883,13 +2715,10 @@
         <v>60</v>
       </c>
       <c r="G72" t="s">
-        <v>72</v>
-      </c>
-      <c r="H72" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>58</v>
       </c>
@@ -2909,13 +2738,10 @@
         <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H73" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>58</v>
       </c>
@@ -2935,13 +2761,10 @@
         <v>63</v>
       </c>
       <c r="G74" t="s">
-        <v>74</v>
-      </c>
-      <c r="H74" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>58</v>
       </c>
@@ -2961,18 +2784,15 @@
         <v>63</v>
       </c>
       <c r="G75" t="s">
-        <v>74</v>
-      </c>
-      <c r="H75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>58</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C76" t="s">
         <v>55</v>
@@ -2984,21 +2804,18 @@
         <v>159.69</v>
       </c>
       <c r="F76" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G76" t="s">
-        <v>78</v>
-      </c>
-      <c r="H76" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>58</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C77" t="s">
         <v>54</v>
@@ -3013,18 +2830,15 @@
         <v>60</v>
       </c>
       <c r="G77" t="s">
-        <v>74</v>
-      </c>
-      <c r="H77" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>58</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
         <v>56</v>
@@ -3036,21 +2850,18 @@
         <v>94.2</v>
       </c>
       <c r="F78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>58</v>
       </c>
       <c r="B79" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
         <v>56</v>
@@ -3062,18 +2873,15 @@
         <v>61.98</v>
       </c>
       <c r="F79" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G79" t="s">
-        <v>74</v>
-      </c>
-      <c r="H79" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B80" t="s">
         <v>59</v>
@@ -3091,15 +2899,12 @@
         <v>60</v>
       </c>
       <c r="G80" t="s">
-        <v>72</v>
-      </c>
-      <c r="H80" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B81" t="s">
         <v>61</v>
@@ -3117,15 +2922,12 @@
         <v>62</v>
       </c>
       <c r="G81" t="s">
-        <v>73</v>
-      </c>
-      <c r="H81" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
         <v>39</v>
@@ -3143,15 +2945,12 @@
         <v>63</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
-      </c>
-      <c r="H82" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
         <v>48</v>
@@ -3169,18 +2968,15 @@
         <v>63</v>
       </c>
       <c r="G83" t="s">
-        <v>74</v>
-      </c>
-      <c r="H83" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B84" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
         <v>55</v>
@@ -3192,21 +2988,18 @@
         <v>159.69</v>
       </c>
       <c r="F84" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>78</v>
-      </c>
-      <c r="H84" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B85" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C85" t="s">
         <v>54</v>
@@ -3221,18 +3014,15 @@
         <v>60</v>
       </c>
       <c r="G85" t="s">
-        <v>74</v>
-      </c>
-      <c r="H85" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B86" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C86" t="s">
         <v>56</v>
@@ -3244,21 +3034,18 @@
         <v>94.2</v>
       </c>
       <c r="F86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
-      </c>
-      <c r="H86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
+        <v>71</v>
+      </c>
+      <c r="B87" t="s">
         <v>70</v>
-      </c>
-      <c r="B87" t="s">
-        <v>69</v>
       </c>
       <c r="C87" t="s">
         <v>56</v>
@@ -3270,13 +3057,240 @@
         <v>61.98</v>
       </c>
       <c r="F87" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G87" t="s">
-        <v>74</v>
-      </c>
-      <c r="H87" t="s">
-        <v>86</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88" t="s">
+        <v>100</v>
+      </c>
+      <c r="C88" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88">
+        <v>100</v>
+      </c>
+      <c r="E88">
+        <v>79.87</v>
+      </c>
+      <c r="F88" t="s">
+        <v>66</v>
+      </c>
+      <c r="G88" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89" t="s">
+        <v>54</v>
+      </c>
+      <c r="D89">
+        <v>100</v>
+      </c>
+      <c r="E89">
+        <v>123.22</v>
+      </c>
+      <c r="F89" t="s">
+        <v>66</v>
+      </c>
+      <c r="G89" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" t="s">
+        <v>105</v>
+      </c>
+      <c r="C90" t="s">
+        <v>54</v>
+      </c>
+      <c r="D90">
+        <v>100</v>
+      </c>
+      <c r="E90">
+        <v>150.71</v>
+      </c>
+      <c r="F90" t="s">
+        <v>66</v>
+      </c>
+      <c r="G90" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>64</v>
+      </c>
+      <c r="B91" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" t="s">
+        <v>55</v>
+      </c>
+      <c r="D91">
+        <v>100</v>
+      </c>
+      <c r="E91">
+        <v>159.69</v>
+      </c>
+      <c r="F91" t="s">
+        <v>66</v>
+      </c>
+      <c r="G91" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" t="s">
+        <v>109</v>
+      </c>
+      <c r="C92" t="s">
+        <v>56</v>
+      </c>
+      <c r="D92">
+        <v>100</v>
+      </c>
+      <c r="E92">
+        <v>74.69</v>
+      </c>
+      <c r="F92" t="s">
+        <v>66</v>
+      </c>
+      <c r="G92" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" t="s">
+        <v>100</v>
+      </c>
+      <c r="C93" t="s">
+        <v>54</v>
+      </c>
+      <c r="D93" s="2">
+        <v>95.2</v>
+      </c>
+      <c r="E93">
+        <v>79.87</v>
+      </c>
+      <c r="F93" t="s">
+        <v>60</v>
+      </c>
+      <c r="G93" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" t="s">
+        <v>54</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="E94">
+        <v>123.22</v>
+      </c>
+      <c r="F94" t="s">
+        <v>66</v>
+      </c>
+      <c r="G94" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" t="s">
+        <v>65</v>
+      </c>
+      <c r="C95" t="s">
+        <v>55</v>
+      </c>
+      <c r="D95" s="2">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="E95">
+        <v>159.69</v>
+      </c>
+      <c r="F95" t="s">
+        <v>66</v>
+      </c>
+      <c r="G95" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" t="s">
+        <v>55</v>
+      </c>
+      <c r="D96" s="2">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="E96">
+        <v>101.96</v>
+      </c>
+      <c r="F96" t="s">
+        <v>62</v>
+      </c>
+      <c r="G96" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" t="s">
+        <v>59</v>
+      </c>
+      <c r="C97" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="2">
+        <v>1.47</v>
+      </c>
+      <c r="E97">
+        <v>60.08</v>
+      </c>
+      <c r="F97" t="s">
+        <v>60</v>
+      </c>
+      <c r="G97" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
